--- a/technology_surveys/023_programming_languages_proficiency_survey--technology_surveys.xlsx
+++ b/technology_surveys/023_programming_languages_proficiency_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>c++</t>
+          <t>swift</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Swift</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>swift</t>
+          <t>ruby</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Ruby</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>survey_language_choices</t>
+          <t>language_proficiency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ruby</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ruby</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>beginner</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>language_proficiency_choices</t>
+          <t>frequency_of_use_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>frequently</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Frequently</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>frequency_of_use_choices</t>
+          <t>favorite_language_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>c++</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>c#</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>C#</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>c#</t>
+          <t>swift</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>Swift</t>
         </is>
       </c>
     </row>
@@ -1522,46 +1522,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>ruby</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Ruby</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>favorite_language_choices</t>
+          <t>favorite_language_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>swift</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>favorite_language_choices</t>
+          <t>favorite_language_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ruby</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ruby</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>c++</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>c#</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C#</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>swift</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Swift</t>
         </is>
       </c>
     </row>
@@ -1658,63 +1658,63 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>c#</t>
+          <t>ruby</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>Ruby</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>favorite_language_2_choices</t>
+          <t>frequency_of_use_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>favorite_language_2_choices</t>
+          <t>frequency_of_use_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>swift</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>favorite_language_2_choices</t>
+          <t>frequency_of_use_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ruby</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ruby</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1743,97 +1743,97 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>frequency_of_use_2_choices</t>
+          <t>other_languages_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>frequency_of_use_2_choices</t>
+          <t>other_languages_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>frequently</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Frequently</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>frequency_of_use_2_choices</t>
+          <t>other_languages_3_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>other_languages_2_choices</t>
+          <t>other_languages_3_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>other_languages_2_choices</t>
+          <t>other_languages_3_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>c++</t>
+          <t>c#</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>C#</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>swift</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Swift</t>
         </is>
       </c>
     </row>
@@ -1913,112 +1913,44 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>javascript</t>
+          <t>ruby</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Ruby</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>other_languages_3_choices</t>
+          <t>other_project_1_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>c#</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>other_languages_3_choices</t>
+          <t>other_project_1_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>other_languages_3_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>swift</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Swift</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>other_languages_3_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>ruby</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ruby</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>other_project_1_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>other_project_1_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
         <is>
           <t>False</t>
         </is>
